--- a/reference_data/clinic_data.xlsx
+++ b/reference_data/clinic_data.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="549">
   <si>
     <t>country</t>
   </si>
   <si>
-    <t>province</t>
+    <t>clinic_province</t>
   </si>
   <si>
     <t>clinic_name</t>
@@ -70,9 +70,6 @@
     <t>TH_CP001</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Nakornping Hospital</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
   </si>
   <si>
     <t>MM_MC001</t>
-  </si>
-  <si>
-    <t>TBC</t>
   </si>
   <si>
     <t>Magwe General Hospital</t>
@@ -837,6 +831,9 @@
   </si>
   <si>
     <t>DATE</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>THAILAND</t>
@@ -2332,9 +2329,7 @@
       <c r="J2" s="10">
         <v>42856.0</v>
       </c>
-      <c r="K2" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K2" s="11"/>
     </row>
     <row r="3">
       <c r="A3" s="6">
@@ -2347,29 +2342,27 @@
         <v>11</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="J3" s="12">
         <v>45170.0</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K3" s="11"/>
     </row>
     <row r="4">
       <c r="A4" s="6">
@@ -2379,25 +2372,25 @@
         <v>10</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="J4" s="16">
         <v>42887.0</v>
@@ -2414,32 +2407,30 @@
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="J5" s="12">
         <v>44652.0</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="6">
@@ -2449,32 +2440,30 @@
         <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="J6" s="12">
         <v>42826.0</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="6">
@@ -2484,25 +2473,25 @@
         <v>10</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="J7" s="16">
         <v>42767.0</v>
@@ -2519,32 +2508,30 @@
         <v>10</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="J8" s="12">
         <v>42795.0</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="6">
@@ -2554,32 +2541,30 @@
         <v>10</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="J9" s="12">
         <v>42826.0</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="6">
@@ -2589,32 +2574,30 @@
         <v>10</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="J10" s="12">
         <v>42826.0</v>
       </c>
-      <c r="K10" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="6">
@@ -2624,25 +2607,25 @@
         <v>10</v>
       </c>
       <c r="C11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="J11" s="16">
         <v>43374.0</v>
@@ -2659,32 +2642,30 @@
         <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="J12" s="17">
         <v>43647.0</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="6">
@@ -2694,32 +2675,30 @@
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="J13" s="17">
         <v>43739.0</v>
       </c>
-      <c r="K13" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="6">
@@ -2729,60 +2708,58 @@
         <v>10</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="J14" s="12">
         <v>45748.0</v>
       </c>
-      <c r="K14" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="6">
         <v>14.0</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="G15" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="I15" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="J15" s="16">
         <v>42767.0</v>
@@ -2796,28 +2773,28 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>79</v>
-      </c>
       <c r="D16" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="G16" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="I16" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="J16" s="16">
         <v>44287.0</v>
@@ -2831,242 +2808,228 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>79</v>
-      </c>
       <c r="D17" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="18" t="s">
+      <c r="I17" s="18" t="s">
         <v>91</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>92</v>
       </c>
       <c r="J17" s="21">
         <v>44927.0</v>
       </c>
-      <c r="K17" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K17" s="22"/>
     </row>
     <row r="18">
       <c r="A18" s="6">
         <v>17.0</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>79</v>
-      </c>
       <c r="D18" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="18" t="s">
+      <c r="I18" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>96</v>
       </c>
       <c r="J18" s="21">
         <v>44927.0</v>
       </c>
-      <c r="K18" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K18" s="22"/>
     </row>
     <row r="19">
       <c r="A19" s="6">
         <v>18.0</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>97</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>98</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="18" t="s">
+      <c r="I19" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>101</v>
       </c>
       <c r="J19" s="21">
         <v>42767.0</v>
       </c>
-      <c r="K19" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K19" s="22"/>
     </row>
     <row r="20">
       <c r="A20" s="6">
         <v>19.0</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="18" t="s">
+      <c r="I20" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>105</v>
       </c>
       <c r="J20" s="21">
         <v>44927.0</v>
       </c>
-      <c r="K20" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K20" s="22"/>
     </row>
     <row r="21">
       <c r="A21" s="6">
         <v>20.0</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G21" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="18" t="s">
+      <c r="I21" s="18" t="s">
         <v>109</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>110</v>
       </c>
       <c r="J21" s="21">
         <v>45108.0</v>
       </c>
-      <c r="K21" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K21" s="22"/>
     </row>
     <row r="22">
       <c r="A22" s="6">
         <v>21.0</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="18" t="s">
+      <c r="I22" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>114</v>
       </c>
       <c r="J22" s="21">
         <v>45566.0</v>
       </c>
-      <c r="K22" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K22" s="22"/>
     </row>
     <row r="23">
       <c r="A23" s="6">
         <v>22.0</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="E23" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="F23" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="G23" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="18" t="s">
+      <c r="I23" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>121</v>
-      </c>
+      <c r="J23" s="22"/>
       <c r="K23" s="22"/>
     </row>
     <row r="24">
@@ -3074,234 +3037,220 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="J24" s="21">
         <v>45261.0</v>
       </c>
-      <c r="K24" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K24" s="22"/>
     </row>
     <row r="25">
       <c r="A25" s="6">
         <v>24.0</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>130</v>
       </c>
       <c r="J25" s="21">
         <v>45292.0</v>
       </c>
-      <c r="K25" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K25" s="22"/>
     </row>
     <row r="26">
       <c r="A26" s="6">
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="I26" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="J26" s="12">
         <v>42401.0</v>
       </c>
-      <c r="K26" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="6">
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="J27" s="12">
         <v>43435.0</v>
       </c>
-      <c r="K27" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="6">
         <v>27.0</v>
       </c>
       <c r="B28" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="20" t="s">
         <v>143</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>145</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="I28" s="18" t="s">
         <v>147</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>149</v>
       </c>
       <c r="J28" s="21">
         <v>42917.0</v>
       </c>
-      <c r="K28" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K28" s="22"/>
     </row>
     <row r="29">
       <c r="A29" s="6">
         <v>28.0</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>154</v>
       </c>
       <c r="J29" s="21">
         <v>44440.0</v>
       </c>
-      <c r="K29" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K29" s="22"/>
     </row>
     <row r="30">
       <c r="A30" s="6">
         <v>29.0</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
-      <c r="J30" s="24" t="s">
-        <v>121</v>
-      </c>
+      <c r="J30" s="24"/>
       <c r="K30" s="25"/>
     </row>
     <row r="31">
@@ -3309,28 +3258,28 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D31" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>158</v>
       </c>
       <c r="J31" s="16">
         <v>44440.0</v>
@@ -3344,767 +3293,723 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="I32" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="J32" s="12">
         <v>43101.0</v>
       </c>
-      <c r="K32" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="6">
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F33" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>170</v>
       </c>
       <c r="J33" s="12">
         <v>43313.0</v>
       </c>
-      <c r="K33" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="6">
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>174</v>
       </c>
       <c r="J34" s="12">
         <v>43313.0</v>
       </c>
-      <c r="K34" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="6">
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="J35" s="12">
         <v>43831.0</v>
       </c>
-      <c r="K35" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="6">
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="J36" s="12">
         <v>44531.0</v>
       </c>
-      <c r="K36" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="6">
         <v>36.0</v>
       </c>
       <c r="B37" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" s="20" t="s">
         <v>183</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>185</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="I37" s="18" t="s">
         <v>187</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>189</v>
       </c>
       <c r="J37" s="21">
         <v>43282.0</v>
       </c>
-      <c r="K37" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K37" s="22"/>
     </row>
     <row r="38">
       <c r="A38" s="6">
         <v>37.0</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" s="18" t="s">
         <v>192</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>194</v>
       </c>
       <c r="J38" s="21">
         <v>43466.0</v>
       </c>
-      <c r="K38" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K38" s="22"/>
     </row>
     <row r="39">
       <c r="A39" s="6">
         <v>38.0</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="I39" s="18" t="s">
         <v>196</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>198</v>
       </c>
       <c r="J39" s="21">
         <v>45170.0</v>
       </c>
-      <c r="K39" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K39" s="22"/>
     </row>
     <row r="40">
       <c r="A40" s="6">
         <v>39.0</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E40" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="I40" s="18" t="s">
         <v>201</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>203</v>
       </c>
       <c r="J40" s="21">
         <v>43556.0</v>
       </c>
-      <c r="K40" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K40" s="22"/>
     </row>
     <row r="41">
       <c r="A41" s="6">
         <v>40.0</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="I41" s="18" t="s">
         <v>205</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>207</v>
       </c>
       <c r="J41" s="21">
         <v>45170.0</v>
       </c>
-      <c r="K41" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K41" s="22"/>
     </row>
     <row r="42">
       <c r="A42" s="6">
         <v>41.0</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="I42" s="18" t="s">
         <v>210</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>212</v>
       </c>
       <c r="J42" s="21">
         <v>44378.0</v>
       </c>
-      <c r="K42" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K42" s="22"/>
     </row>
     <row r="43">
       <c r="A43" s="6">
         <v>42.0</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="I43" s="18" t="s">
         <v>215</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>217</v>
       </c>
       <c r="J43" s="21">
         <v>44348.0</v>
       </c>
-      <c r="K43" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="K43" s="22"/>
     </row>
     <row r="44">
       <c r="A44" s="6">
         <v>43.0</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>223</v>
       </c>
       <c r="J44" s="12">
         <v>45413.0</v>
       </c>
-      <c r="K44" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="6">
         <v>44.0</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="J45" s="12">
         <v>45505.0</v>
       </c>
-      <c r="K45" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="6">
         <v>45.0</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J46" s="12">
         <v>45597.0</v>
       </c>
-      <c r="K46" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="6">
         <v>46.0</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>235</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>237</v>
       </c>
       <c r="J47" s="12">
         <v>45627.0</v>
       </c>
-      <c r="K47" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="6">
         <v>47.0</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="J48" s="12">
         <v>45658.0</v>
       </c>
-      <c r="K48" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="6">
         <v>48.0</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="J49" s="12">
         <v>45658.0</v>
       </c>
-      <c r="K49" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="6">
         <v>49.0</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J50" s="12">
         <v>45778.0</v>
       </c>
-      <c r="K50" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="6">
         <v>50.0</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="J51" s="12">
         <v>45809.0</v>
       </c>
-      <c r="K51" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="6">
         <v>51.0</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J52" s="12">
         <v>45809.0</v>
       </c>
-      <c r="K52" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="K52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="6">
         <v>52.0</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="G53" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E53" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F53" s="7" t="s">
+      <c r="I53" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>121</v>
-      </c>
+      <c r="J53" s="11"/>
       <c r="K53" s="11"/>
     </row>
     <row r="54">
@@ -13637,35 +13542,35 @@
     <row r="1" ht="23.25" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="Q1" s="30"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
       <c r="F2" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H2" s="31">
         <v>2017.0</v>
@@ -13716,7 +13621,7 @@
         <v>42856.0</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H3" s="32" t="b">
         <v>0</v>
@@ -13757,7 +13662,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
@@ -13766,7 +13671,7 @@
         <v>45170.0</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H4" s="32"/>
       <c r="N4" s="33" t="b">
@@ -13787,13 +13692,13 @@
         <v>10</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="16">
         <v>42887.0</v>
@@ -13833,10 +13738,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
@@ -13845,7 +13750,7 @@
         <v>44652.0</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H6" s="32"/>
       <c r="M6" s="33" t="b">
@@ -13869,10 +13774,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
@@ -13881,7 +13786,7 @@
         <v>42826.0</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H7" s="32" t="b">
         <v>0</v>
@@ -13919,13 +13824,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>39</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="16">
         <v>42767.0</v>
@@ -13970,10 +13875,10 @@
         <v>10</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
@@ -13982,7 +13887,7 @@
         <v>42795.0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H9" s="32" t="b">
         <v>0</v>
@@ -14020,10 +13925,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
@@ -14032,7 +13937,7 @@
         <v>42826.0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H10" s="32" t="b">
         <v>0</v>
@@ -14070,10 +13975,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
@@ -14082,7 +13987,7 @@
         <v>42826.0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H11" s="32" t="b">
         <v>0</v>
@@ -14120,13 +14025,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>59</v>
-      </c>
       <c r="E12" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="16">
         <v>43374.0</v>
@@ -14163,10 +14068,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -14175,7 +14080,7 @@
         <v>43647.0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H13" s="32"/>
       <c r="J13" s="32" t="b">
@@ -14208,10 +14113,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
@@ -14220,7 +14125,7 @@
         <v>43739.0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H14" s="33"/>
       <c r="J14" s="32" t="b">
@@ -14253,10 +14158,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -14265,7 +14170,7 @@
         <v>45748.0</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H15" s="32"/>
       <c r="P15" s="34" t="b">
@@ -14277,16 +14182,16 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>80</v>
-      </c>
       <c r="E16" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="16">
         <v>42767.0</v>
@@ -14322,16 +14227,16 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>79</v>
-      </c>
       <c r="D17" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="16">
         <v>44287.0</v>
@@ -14359,13 +14264,13 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>79</v>
-      </c>
       <c r="D18" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>13</v>
@@ -14374,7 +14279,7 @@
         <v>44927.0</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H18" s="38"/>
       <c r="N18" s="39" t="b">
@@ -14392,13 +14297,13 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>79</v>
-      </c>
       <c r="D19" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>13</v>
@@ -14407,7 +14312,7 @@
         <v>44927.0</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H19" s="38"/>
       <c r="N19" s="39" t="b">
@@ -14425,13 +14330,13 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>97</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>98</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>13</v>
@@ -14440,7 +14345,7 @@
         <v>42767.0</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H20" s="39" t="b">
         <v>1</v>
@@ -14475,13 +14380,13 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>13</v>
@@ -14490,7 +14395,7 @@
         <v>44927.0</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H21" s="38"/>
       <c r="N21" s="39" t="b">
@@ -14508,13 +14413,13 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>13</v>
@@ -14523,7 +14428,7 @@
         <v>45108.0</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H22" s="38"/>
       <c r="N22" s="39" t="b">
@@ -14541,13 +14446,13 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>13</v>
@@ -14556,7 +14461,7 @@
         <v>45566.0</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H23" s="38"/>
       <c r="O23" s="39" t="b">
@@ -14571,13 +14476,13 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>13</v>
@@ -14586,7 +14491,7 @@
         <v>45261.0</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H24" s="38"/>
       <c r="N24" s="39" t="b">
@@ -14604,13 +14509,13 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>13</v>
@@ -14619,7 +14524,7 @@
         <v>45292.0</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H25" s="38"/>
       <c r="O25" s="39" t="b">
@@ -14634,13 +14539,13 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
@@ -14649,7 +14554,7 @@
         <v>42401.0</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H26" s="33" t="b">
         <v>1</v>
@@ -14684,13 +14589,13 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>13</v>
@@ -14699,7 +14604,7 @@
         <v>43435.0</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="33" t="b">
@@ -14732,13 +14637,13 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="20" t="s">
         <v>143</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>145</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>13</v>
@@ -14747,7 +14652,7 @@
         <v>42917.0</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H28" s="39" t="b">
         <v>1</v>
@@ -14782,13 +14687,13 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>13</v>
@@ -14797,7 +14702,7 @@
         <v>44440.0</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H29" s="38"/>
       <c r="L29" s="39" t="b">
@@ -14821,16 +14726,16 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" s="16">
         <v>44440.0</v>
@@ -14859,13 +14764,13 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>13</v>
@@ -14874,7 +14779,7 @@
         <v>43101.0</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="33" t="b">
@@ -14907,13 +14812,13 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>13</v>
@@ -14922,7 +14827,7 @@
         <v>43313.0</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H32" s="33"/>
       <c r="I32" s="33" t="b">
@@ -14955,13 +14860,13 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>13</v>
@@ -14970,7 +14875,7 @@
         <v>43313.0</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="33" t="b">
@@ -15003,13 +14908,13 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>13</v>
@@ -15018,7 +14923,7 @@
         <v>43831.0</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H34" s="32"/>
       <c r="K34" s="33" t="b">
@@ -15045,13 +14950,13 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>13</v>
@@ -15060,7 +14965,7 @@
         <v>44531.0</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H35" s="32"/>
       <c r="L35" s="33" t="b">
@@ -15084,13 +14989,13 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="20" t="s">
         <v>183</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>185</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>13</v>
@@ -15099,7 +15004,7 @@
         <v>43282.0</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H36" s="39"/>
       <c r="I36" s="39" t="b">
@@ -15132,13 +15037,13 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>13</v>
@@ -15147,7 +15052,7 @@
         <v>43466.0</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H37" s="38"/>
       <c r="J37" s="39" t="b">
@@ -15177,13 +15082,13 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E38" s="18" t="s">
         <v>13</v>
@@ -15192,7 +15097,7 @@
         <v>45170.0</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H38" s="38"/>
       <c r="N38" s="39" t="b">
@@ -15210,13 +15115,13 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>13</v>
@@ -15225,7 +15130,7 @@
         <v>43556.0</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H39" s="38"/>
       <c r="J39" s="39" t="b">
@@ -15255,13 +15160,13 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E40" s="18" t="s">
         <v>13</v>
@@ -15270,7 +15175,7 @@
         <v>45170.0</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H40" s="38"/>
       <c r="N40" s="39" t="b">
@@ -15288,13 +15193,13 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>13</v>
@@ -15303,7 +15208,7 @@
         <v>44378.0</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H41" s="38"/>
       <c r="L41" s="39" t="b">
@@ -15327,13 +15232,13 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>13</v>
@@ -15342,7 +15247,7 @@
         <v>44348.0</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H42" s="38"/>
       <c r="L42" s="39" t="b">
@@ -15366,13 +15271,13 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>13</v>
@@ -15381,7 +15286,7 @@
         <v>45413.0</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H43" s="32"/>
       <c r="O43" s="33" t="b">
@@ -15396,13 +15301,13 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
@@ -15411,7 +15316,7 @@
         <v>45505.0</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H44" s="32"/>
       <c r="O44" s="33" t="b">
@@ -15426,13 +15331,13 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
@@ -15441,7 +15346,7 @@
         <v>45597.0</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H45" s="32"/>
       <c r="O45" s="33" t="b">
@@ -15456,13 +15361,13 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>13</v>
@@ -15471,7 +15376,7 @@
         <v>45627.0</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H46" s="33"/>
       <c r="O46" s="33" t="b">
@@ -15486,20 +15391,20 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="40"/>
       <c r="G47" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H47" s="7"/>
       <c r="P47" s="34" t="b">
@@ -15511,20 +15416,20 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="40"/>
       <c r="G48" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H48" s="7"/>
       <c r="P48" s="34" t="b">
@@ -15536,7 +15441,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="29"/>
@@ -15545,7 +15450,7 @@
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H49" s="7"/>
     </row>
@@ -15554,7 +15459,7 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C50" s="28"/>
       <c r="D50" s="29"/>
@@ -15563,7 +15468,7 @@
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H50" s="7"/>
     </row>
@@ -15572,7 +15477,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C51" s="28"/>
       <c r="D51" s="29"/>
@@ -15581,7 +15486,7 @@
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="11" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="H51" s="7"/>
     </row>
@@ -22328,7 +22233,7 @@
       </c>
       <c r="C1" s="42" t="str">
         <f>Clinic_List!C1</f>
-        <v>province</v>
+        <v>clinic_province</v>
       </c>
       <c r="D1" s="43" t="str">
         <f>Clinic_List!D1</f>
@@ -23925,7 +23830,7 @@
       </c>
       <c r="E52" s="61" t="str">
         <f>Clinic_List!J53</f>
-        <v>TBC</v>
+        <v/>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="54"/>
@@ -38263,29 +38168,29 @@
     <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="66"/>
       <c r="B1" s="67" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="D1" s="67" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="E1" s="67" t="s">
         <v>276</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="F1" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="G1" s="67" t="s">
         <v>278</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="H1" s="68" t="s">
         <v>279</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>280</v>
       </c>
       <c r="I1" s="69"/>
       <c r="J1" s="70" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -38293,25 +38198,25 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="D2" s="72" t="s">
         <v>283</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="E2" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="F2" s="72" t="s">
         <v>285</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="G2" s="72" t="s">
         <v>286</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="H2" s="73" t="s">
         <v>287</v>
-      </c>
-      <c r="H2" s="73" t="s">
-        <v>288</v>
       </c>
       <c r="I2" s="74"/>
       <c r="J2" s="74"/>
@@ -38321,25 +38226,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="72" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="D3" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="E3" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="F3" s="72" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="G3" s="72" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="H3" s="73" t="s">
         <v>294</v>
-      </c>
-      <c r="H3" s="73" t="s">
-        <v>295</v>
       </c>
       <c r="I3" s="74"/>
       <c r="J3" s="74"/>
@@ -38349,25 +38254,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="E4" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="F4" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="G4" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="H4" s="73" t="s">
         <v>300</v>
-      </c>
-      <c r="H4" s="73" t="s">
-        <v>301</v>
       </c>
       <c r="I4" s="74"/>
       <c r="J4" s="74"/>
@@ -38377,25 +38282,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="D5" s="72" t="s">
         <v>303</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="E5" s="72" t="s">
         <v>304</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="F5" s="72" t="s">
         <v>305</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="G5" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="H5" s="73" t="s">
         <v>307</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>308</v>
       </c>
       <c r="I5" s="74"/>
       <c r="J5" s="74"/>
@@ -38405,25 +38310,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="72" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="D6" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="E6" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="F6" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="G6" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="H6" s="73" t="s">
         <v>314</v>
-      </c>
-      <c r="H6" s="73" t="s">
-        <v>315</v>
       </c>
       <c r="I6" s="74"/>
       <c r="J6" s="74"/>
@@ -38433,25 +38338,25 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="72" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="D7" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="E7" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="E7" s="72" t="s">
+      <c r="F7" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="G7" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="H7" s="73" t="s">
         <v>321</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>322</v>
       </c>
       <c r="I7" s="74"/>
       <c r="J7" s="74"/>
@@ -38461,25 +38366,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="72" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="D8" s="72" t="s">
         <v>324</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="E8" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="F8" s="72" t="s">
         <v>326</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="G8" s="72" t="s">
         <v>327</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="H8" s="73" t="s">
         <v>328</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>329</v>
       </c>
       <c r="I8" s="74"/>
       <c r="J8" s="74"/>
@@ -38489,25 +38394,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="72" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="C9" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="72" t="s">
+      <c r="E9" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="F9" s="72" t="s">
         <v>332</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="G9" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="H9" s="73" t="s">
         <v>334</v>
-      </c>
-      <c r="H9" s="73" t="s">
-        <v>335</v>
       </c>
       <c r="I9" s="74"/>
       <c r="J9" s="74"/>
@@ -38517,25 +38422,25 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="72" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="72" t="s">
         <v>336</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="D10" s="72" t="s">
         <v>337</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="E10" s="72" t="s">
         <v>338</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="F10" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="G10" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="73" t="s">
         <v>340</v>
-      </c>
-      <c r="G10" s="72" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="73" t="s">
-        <v>341</v>
       </c>
       <c r="I10" s="74"/>
       <c r="J10" s="74"/>
@@ -38548,22 +38453,22 @@
         <v>11</v>
       </c>
       <c r="C11" s="72" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="E11" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="F11" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="G11" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="H11" s="73" t="s">
         <v>346</v>
-      </c>
-      <c r="H11" s="73" t="s">
-        <v>347</v>
       </c>
       <c r="I11" s="74"/>
       <c r="J11" s="74"/>
@@ -38573,25 +38478,25 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="72" t="s">
+        <v>347</v>
+      </c>
+      <c r="C12" s="72" t="s">
         <v>348</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="D12" s="72" t="s">
         <v>349</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="E12" s="72" t="s">
         <v>350</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="F12" s="72" t="s">
         <v>351</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="G12" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="G12" s="72" t="s">
+      <c r="H12" s="73" t="s">
         <v>353</v>
-      </c>
-      <c r="H12" s="73" t="s">
-        <v>354</v>
       </c>
       <c r="I12" s="74"/>
       <c r="J12" s="74"/>
@@ -38601,25 +38506,25 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="72" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="72" t="s">
         <v>355</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="D13" s="72" t="s">
         <v>356</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="E13" s="72" t="s">
         <v>357</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="F13" s="72" t="s">
         <v>358</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="G13" s="72" t="s">
         <v>359</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="H13" s="73" t="s">
         <v>360</v>
-      </c>
-      <c r="H13" s="73" t="s">
-        <v>361</v>
       </c>
       <c r="I13" s="74"/>
       <c r="J13" s="74"/>
@@ -38629,25 +38534,25 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="C14" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="D14" s="72" t="s">
         <v>363</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="E14" s="72" t="s">
         <v>364</v>
       </c>
-      <c r="E14" s="72" t="s">
+      <c r="F14" s="72" t="s">
         <v>365</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="G14" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="73" t="s">
         <v>366</v>
-      </c>
-      <c r="G14" s="72" t="s">
-        <v>213</v>
-      </c>
-      <c r="H14" s="73" t="s">
-        <v>367</v>
       </c>
       <c r="I14" s="74"/>
       <c r="J14" s="74"/>
@@ -38657,25 +38562,25 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="72" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" s="72" t="s">
         <v>368</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="D15" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="E15" s="72" t="s">
         <v>370</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="F15" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="G15" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="73" t="s">
         <v>372</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="H15" s="73" t="s">
-        <v>373</v>
       </c>
       <c r="I15" s="74"/>
       <c r="J15" s="74"/>
@@ -38685,25 +38590,25 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="72" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="C16" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="72" t="s">
+      <c r="E16" s="72" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="72" t="s">
         <v>375</v>
       </c>
-      <c r="E16" s="72" t="s">
-        <v>166</v>
-      </c>
-      <c r="F16" s="72" t="s">
+      <c r="G16" s="72" t="s">
         <v>376</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="H16" s="73" t="s">
         <v>377</v>
-      </c>
-      <c r="H16" s="73" t="s">
-        <v>378</v>
       </c>
       <c r="I16" s="74"/>
       <c r="J16" s="74"/>
@@ -38713,23 +38618,23 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="72" t="s">
+        <v>378</v>
+      </c>
+      <c r="D17" s="72" t="s">
         <v>379</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="E17" s="72" t="s">
         <v>380</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>381</v>
       </c>
       <c r="F17" s="73"/>
       <c r="G17" s="72" t="s">
+        <v>381</v>
+      </c>
+      <c r="H17" s="73" t="s">
         <v>382</v>
-      </c>
-      <c r="H17" s="73" t="s">
-        <v>383</v>
       </c>
       <c r="I17" s="74"/>
       <c r="J17" s="74"/>
@@ -38739,21 +38644,21 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="72" t="s">
+        <v>383</v>
+      </c>
+      <c r="D18" s="72" t="s">
         <v>384</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="E18" s="72" t="s">
         <v>385</v>
-      </c>
-      <c r="E18" s="72" t="s">
-        <v>386</v>
       </c>
       <c r="F18" s="73"/>
       <c r="G18" s="73"/>
       <c r="H18" s="73" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I18" s="74"/>
       <c r="J18" s="74"/>
@@ -38763,21 +38668,21 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="72" t="s">
+        <v>387</v>
+      </c>
+      <c r="C19" s="72" t="s">
         <v>388</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="D19" s="72" t="s">
         <v>389</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="E19" s="72" t="s">
         <v>390</v>
-      </c>
-      <c r="E19" s="72" t="s">
-        <v>391</v>
       </c>
       <c r="F19" s="73"/>
       <c r="G19" s="73"/>
       <c r="H19" s="73" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I19" s="74"/>
       <c r="J19" s="74"/>
@@ -38787,19 +38692,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C20" s="73"/>
       <c r="D20" s="72" t="s">
+        <v>393</v>
+      </c>
+      <c r="E20" s="72" t="s">
         <v>394</v>
-      </c>
-      <c r="E20" s="72" t="s">
-        <v>395</v>
       </c>
       <c r="F20" s="73"/>
       <c r="G20" s="73"/>
       <c r="H20" s="73" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I20" s="74"/>
       <c r="J20" s="74"/>
@@ -38809,19 +38714,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C21" s="73"/>
       <c r="D21" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="E21" s="72" t="s">
         <v>398</v>
-      </c>
-      <c r="E21" s="72" t="s">
-        <v>399</v>
       </c>
       <c r="F21" s="73"/>
       <c r="G21" s="73"/>
       <c r="H21" s="73" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I21" s="74"/>
       <c r="J21" s="74"/>
@@ -38831,19 +38736,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C22" s="73"/>
       <c r="D22" s="72" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E22" s="72" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F22" s="73"/>
       <c r="G22" s="73"/>
       <c r="H22" s="73" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I22" s="74"/>
       <c r="J22" s="74"/>
@@ -38853,19 +38758,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="72" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C23" s="73"/>
       <c r="D23" s="72" t="s">
+        <v>404</v>
+      </c>
+      <c r="E23" s="72" t="s">
         <v>405</v>
-      </c>
-      <c r="E23" s="72" t="s">
-        <v>406</v>
       </c>
       <c r="F23" s="73"/>
       <c r="G23" s="73"/>
       <c r="H23" s="73" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I23" s="74"/>
       <c r="J23" s="74"/>
@@ -38875,19 +38780,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="72" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C24" s="73"/>
       <c r="D24" s="72" t="s">
+        <v>408</v>
+      </c>
+      <c r="E24" s="72" t="s">
         <v>409</v>
-      </c>
-      <c r="E24" s="72" t="s">
-        <v>410</v>
       </c>
       <c r="F24" s="73"/>
       <c r="G24" s="73"/>
       <c r="H24" s="73" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I24" s="74"/>
       <c r="J24" s="74"/>
@@ -38897,19 +38802,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="72" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C25" s="73"/>
       <c r="D25" s="72" t="s">
+        <v>412</v>
+      </c>
+      <c r="E25" s="72" t="s">
         <v>413</v>
-      </c>
-      <c r="E25" s="72" t="s">
-        <v>414</v>
       </c>
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
       <c r="H25" s="73" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I25" s="74"/>
       <c r="J25" s="74"/>
@@ -38919,19 +38824,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="73"/>
       <c r="D26" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="E26" s="72" t="s">
         <v>416</v>
-      </c>
-      <c r="E26" s="72" t="s">
-        <v>417</v>
       </c>
       <c r="F26" s="73"/>
       <c r="G26" s="73"/>
       <c r="H26" s="73" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I26" s="74"/>
       <c r="J26" s="74"/>
@@ -38941,17 +38846,17 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="72" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C27" s="73"/>
       <c r="D27" s="72" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E27" s="73"/>
       <c r="F27" s="73"/>
       <c r="G27" s="73"/>
       <c r="H27" s="73" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I27" s="74"/>
       <c r="J27" s="74"/>
@@ -38961,17 +38866,17 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="72" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C28" s="73"/>
       <c r="D28" s="72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E28" s="73"/>
       <c r="F28" s="73"/>
       <c r="G28" s="73"/>
       <c r="H28" s="73" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I28" s="74"/>
       <c r="J28" s="74"/>
@@ -38981,17 +38886,17 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C29" s="73"/>
       <c r="D29" s="72" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E29" s="73"/>
       <c r="F29" s="73"/>
       <c r="G29" s="73"/>
       <c r="H29" s="73" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I29" s="74"/>
       <c r="J29" s="74"/>
@@ -39001,17 +38906,17 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C30" s="73"/>
       <c r="D30" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E30" s="73"/>
       <c r="F30" s="73"/>
       <c r="G30" s="73"/>
       <c r="H30" s="73" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I30" s="74"/>
       <c r="J30" s="74"/>
@@ -39021,17 +38926,17 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="72" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E31" s="73"/>
       <c r="F31" s="73"/>
       <c r="G31" s="73"/>
       <c r="H31" s="73" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I31" s="74"/>
       <c r="J31" s="74"/>
@@ -39041,17 +38946,17 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="73"/>
       <c r="D32" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E32" s="73"/>
       <c r="F32" s="73"/>
       <c r="G32" s="73"/>
       <c r="H32" s="73" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I32" s="74"/>
       <c r="J32" s="74"/>
@@ -39061,17 +38966,17 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C33" s="73"/>
       <c r="D33" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E33" s="73"/>
       <c r="F33" s="73"/>
       <c r="G33" s="73"/>
       <c r="H33" s="73" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I33" s="74"/>
       <c r="J33" s="74"/>
@@ -39081,17 +38986,17 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C34" s="73"/>
       <c r="D34" s="72" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E34" s="73"/>
       <c r="F34" s="73"/>
       <c r="G34" s="73"/>
       <c r="H34" s="73" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I34" s="74"/>
       <c r="J34" s="74"/>
@@ -39101,17 +39006,17 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="72" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C35" s="73"/>
       <c r="D35" s="72" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="73"/>
       <c r="H35" s="73" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I35" s="74"/>
       <c r="J35" s="74"/>
@@ -39121,17 +39026,17 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="72" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C36" s="73"/>
       <c r="D36" s="72" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E36" s="73"/>
       <c r="F36" s="73"/>
       <c r="G36" s="73"/>
       <c r="H36" s="73" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I36" s="74"/>
       <c r="J36" s="74"/>
@@ -39141,17 +39046,17 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="72" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C37" s="73"/>
       <c r="D37" s="72" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E37" s="73"/>
       <c r="F37" s="73"/>
       <c r="G37" s="73"/>
       <c r="H37" s="73" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I37" s="74"/>
       <c r="J37" s="74"/>
@@ -39161,17 +39066,17 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="72" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C38" s="73"/>
       <c r="D38" s="72" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E38" s="73"/>
       <c r="F38" s="73"/>
       <c r="G38" s="73"/>
       <c r="H38" s="73" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I38" s="74"/>
       <c r="J38" s="74"/>
@@ -39181,17 +39086,17 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="72" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C39" s="73"/>
       <c r="D39" s="72" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E39" s="73"/>
       <c r="F39" s="73"/>
       <c r="G39" s="73"/>
       <c r="H39" s="73" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I39" s="74"/>
       <c r="J39" s="74"/>
@@ -39201,17 +39106,17 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="72" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C40" s="73"/>
       <c r="D40" s="72" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E40" s="73"/>
       <c r="F40" s="73"/>
       <c r="G40" s="73"/>
       <c r="H40" s="73" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I40" s="74"/>
       <c r="J40" s="74"/>
@@ -39221,17 +39126,17 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="72" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C41" s="73"/>
       <c r="D41" s="72" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E41" s="73"/>
       <c r="F41" s="73"/>
       <c r="G41" s="73"/>
       <c r="H41" s="73" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I41" s="74"/>
       <c r="J41" s="74"/>
@@ -39241,17 +39146,17 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C42" s="73"/>
       <c r="D42" s="72" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E42" s="73"/>
       <c r="F42" s="73"/>
       <c r="G42" s="73"/>
       <c r="H42" s="73" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I42" s="74"/>
       <c r="J42" s="74"/>
@@ -39261,17 +39166,17 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="72" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C43" s="73"/>
       <c r="D43" s="72" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E43" s="73"/>
       <c r="F43" s="73"/>
       <c r="G43" s="73"/>
       <c r="H43" s="73" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I43" s="74"/>
       <c r="J43" s="74"/>
@@ -39281,17 +39186,17 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="72" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C44" s="73"/>
       <c r="D44" s="72" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E44" s="73"/>
       <c r="F44" s="73"/>
       <c r="G44" s="73"/>
       <c r="H44" s="73" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I44" s="74"/>
       <c r="J44" s="74"/>
@@ -39301,17 +39206,17 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="72" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C45" s="73"/>
       <c r="D45" s="72" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E45" s="73"/>
       <c r="F45" s="73"/>
       <c r="G45" s="73"/>
       <c r="H45" s="73" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I45" s="74"/>
       <c r="J45" s="74"/>
@@ -39321,17 +39226,17 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="72" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C46" s="73"/>
       <c r="D46" s="72" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E46" s="73"/>
       <c r="F46" s="73"/>
       <c r="G46" s="73"/>
       <c r="H46" s="73" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I46" s="74"/>
       <c r="J46" s="74"/>
@@ -39341,17 +39246,17 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="72" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C47" s="73"/>
       <c r="D47" s="72" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E47" s="73"/>
       <c r="F47" s="73"/>
       <c r="G47" s="73"/>
       <c r="H47" s="73" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I47" s="74"/>
       <c r="J47" s="74"/>
@@ -39361,17 +39266,17 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="72" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C48" s="73"/>
       <c r="D48" s="72" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E48" s="73"/>
       <c r="F48" s="73"/>
       <c r="G48" s="73"/>
       <c r="H48" s="73" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I48" s="74"/>
       <c r="J48" s="74"/>
@@ -39381,17 +39286,17 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="72" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C49" s="73"/>
       <c r="D49" s="72" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E49" s="73"/>
       <c r="F49" s="73"/>
       <c r="G49" s="73"/>
       <c r="H49" s="73" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I49" s="74"/>
       <c r="J49" s="74"/>
@@ -39401,17 +39306,17 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="72" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C50" s="73"/>
       <c r="D50" s="72" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E50" s="73"/>
       <c r="F50" s="73"/>
       <c r="G50" s="73"/>
       <c r="H50" s="73" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I50" s="74"/>
       <c r="J50" s="74"/>
@@ -39421,17 +39326,17 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="72" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C51" s="73"/>
       <c r="D51" s="72" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E51" s="73"/>
       <c r="F51" s="73"/>
       <c r="G51" s="73"/>
       <c r="H51" s="73" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I51" s="74"/>
       <c r="J51" s="74"/>
@@ -39441,17 +39346,17 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C52" s="73"/>
       <c r="D52" s="72" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E52" s="73"/>
       <c r="F52" s="73"/>
       <c r="G52" s="73"/>
       <c r="H52" s="73" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I52" s="74"/>
       <c r="J52" s="74"/>
@@ -39461,17 +39366,17 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="72" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C53" s="73"/>
       <c r="D53" s="72" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E53" s="73"/>
       <c r="F53" s="73"/>
       <c r="G53" s="73"/>
       <c r="H53" s="73" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I53" s="74"/>
       <c r="J53" s="74"/>
@@ -39481,17 +39386,17 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="72" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C54" s="73"/>
       <c r="D54" s="72" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E54" s="73"/>
       <c r="F54" s="73"/>
       <c r="G54" s="73"/>
       <c r="H54" s="73" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I54" s="74"/>
       <c r="J54" s="74"/>
@@ -39501,17 +39406,17 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="72" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C55" s="73"/>
       <c r="D55" s="72" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E55" s="73"/>
       <c r="F55" s="73"/>
       <c r="G55" s="73"/>
       <c r="H55" s="73" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I55" s="74"/>
       <c r="J55" s="74"/>
@@ -39521,17 +39426,17 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="72" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C56" s="73"/>
       <c r="D56" s="72" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E56" s="73"/>
       <c r="F56" s="73"/>
       <c r="G56" s="73"/>
       <c r="H56" s="73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I56" s="74"/>
       <c r="J56" s="74"/>
@@ -39541,17 +39446,17 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="72" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C57" s="73"/>
       <c r="D57" s="72" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E57" s="73"/>
       <c r="F57" s="73"/>
       <c r="G57" s="73"/>
       <c r="H57" s="73" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I57" s="74"/>
       <c r="J57" s="74"/>
@@ -39561,17 +39466,17 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="72" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C58" s="73"/>
       <c r="D58" s="72" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E58" s="73"/>
       <c r="F58" s="73"/>
       <c r="G58" s="73"/>
       <c r="H58" s="73" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I58" s="74"/>
       <c r="J58" s="74"/>
@@ -39581,17 +39486,17 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="72" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C59" s="73"/>
       <c r="D59" s="72" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E59" s="73"/>
       <c r="F59" s="73"/>
       <c r="G59" s="73"/>
       <c r="H59" s="73" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I59" s="74"/>
       <c r="J59" s="74"/>
@@ -39601,17 +39506,17 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="72" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C60" s="73"/>
       <c r="D60" s="72" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E60" s="73"/>
       <c r="F60" s="73"/>
       <c r="G60" s="73"/>
       <c r="H60" s="73" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I60" s="74"/>
       <c r="J60" s="74"/>
@@ -39621,17 +39526,17 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="72" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C61" s="73"/>
       <c r="D61" s="72" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E61" s="73"/>
       <c r="F61" s="73"/>
       <c r="G61" s="73"/>
       <c r="H61" s="73" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I61" s="74"/>
       <c r="J61" s="74"/>
@@ -39641,17 +39546,17 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="72" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C62" s="73"/>
       <c r="D62" s="72" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E62" s="73"/>
       <c r="F62" s="73"/>
       <c r="G62" s="73"/>
       <c r="H62" s="73" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I62" s="74"/>
       <c r="J62" s="74"/>
@@ -39661,17 +39566,17 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C63" s="73"/>
       <c r="D63" s="72" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E63" s="73"/>
       <c r="F63" s="73"/>
       <c r="G63" s="73"/>
       <c r="H63" s="73" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I63" s="74"/>
       <c r="J63" s="74"/>
@@ -39681,17 +39586,17 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C64" s="73"/>
       <c r="D64" s="72" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E64" s="73"/>
       <c r="F64" s="73"/>
       <c r="G64" s="73"/>
       <c r="H64" s="73" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I64" s="74"/>
       <c r="J64" s="74"/>
@@ -39701,7 +39606,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="72" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C65" s="73"/>
       <c r="D65" s="73"/>
@@ -39709,7 +39614,7 @@
       <c r="F65" s="73"/>
       <c r="G65" s="73"/>
       <c r="H65" s="73" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I65" s="74"/>
       <c r="J65" s="74"/>
@@ -39719,7 +39624,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="72" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C66" s="73"/>
       <c r="D66" s="73"/>
@@ -39727,7 +39632,7 @@
       <c r="F66" s="73"/>
       <c r="G66" s="73"/>
       <c r="H66" s="73" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I66" s="74"/>
       <c r="J66" s="74"/>
@@ -39737,7 +39642,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="72" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C67" s="73"/>
       <c r="D67" s="73"/>
@@ -39745,7 +39650,7 @@
       <c r="F67" s="73"/>
       <c r="G67" s="73"/>
       <c r="H67" s="73" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I67" s="74"/>
       <c r="J67" s="74"/>
@@ -39755,7 +39660,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="72" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C68" s="73"/>
       <c r="D68" s="73"/>
@@ -39763,7 +39668,7 @@
       <c r="F68" s="73"/>
       <c r="G68" s="73"/>
       <c r="H68" s="73" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I68" s="74"/>
       <c r="J68" s="74"/>
@@ -39773,7 +39678,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C69" s="73"/>
       <c r="D69" s="73"/>
@@ -39781,7 +39686,7 @@
       <c r="F69" s="73"/>
       <c r="G69" s="73"/>
       <c r="H69" s="73" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I69" s="74"/>
       <c r="J69" s="74"/>
@@ -39791,7 +39696,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C70" s="73"/>
       <c r="D70" s="73"/>
@@ -39799,7 +39704,7 @@
       <c r="F70" s="73"/>
       <c r="G70" s="73"/>
       <c r="H70" s="73" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I70" s="74"/>
       <c r="J70" s="74"/>
@@ -39809,7 +39714,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="72" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C71" s="73"/>
       <c r="D71" s="73"/>
@@ -39817,7 +39722,7 @@
       <c r="F71" s="73"/>
       <c r="G71" s="73"/>
       <c r="H71" s="73" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I71" s="74"/>
       <c r="J71" s="74"/>
@@ -39827,7 +39732,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="72" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C72" s="73"/>
       <c r="D72" s="73"/>
@@ -39835,7 +39740,7 @@
       <c r="F72" s="73"/>
       <c r="G72" s="73"/>
       <c r="H72" s="73" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I72" s="74"/>
       <c r="J72" s="74"/>
@@ -39845,7 +39750,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="72" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C73" s="73"/>
       <c r="D73" s="73"/>
@@ -39853,7 +39758,7 @@
       <c r="F73" s="73"/>
       <c r="G73" s="73"/>
       <c r="H73" s="73" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I73" s="74"/>
       <c r="J73" s="74"/>
@@ -39869,7 +39774,7 @@
       <c r="F74" s="73"/>
       <c r="G74" s="73"/>
       <c r="H74" s="73" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I74" s="74"/>
       <c r="J74" s="74"/>
@@ -39885,7 +39790,7 @@
       <c r="F75" s="73"/>
       <c r="G75" s="73"/>
       <c r="H75" s="73" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I75" s="74"/>
       <c r="J75" s="74"/>
@@ -39901,7 +39806,7 @@
       <c r="F76" s="73"/>
       <c r="G76" s="73"/>
       <c r="H76" s="73" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I76" s="74"/>
       <c r="J76" s="74"/>
@@ -39917,7 +39822,7 @@
       <c r="F77" s="73"/>
       <c r="G77" s="73"/>
       <c r="H77" s="73" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I77" s="74"/>
       <c r="J77" s="74"/>
@@ -39933,7 +39838,7 @@
       <c r="F78" s="73"/>
       <c r="G78" s="73"/>
       <c r="H78" s="73" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I78" s="74"/>
       <c r="J78" s="74"/>
@@ -39949,7 +39854,7 @@
       <c r="F79" s="73"/>
       <c r="G79" s="73"/>
       <c r="H79" s="73" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I79" s="74"/>
       <c r="J79" s="74"/>
@@ -39965,7 +39870,7 @@
       <c r="F80" s="73"/>
       <c r="G80" s="73"/>
       <c r="H80" s="73" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I80" s="74"/>
       <c r="J80" s="74"/>
@@ -39981,7 +39886,7 @@
       <c r="F81" s="73"/>
       <c r="G81" s="73"/>
       <c r="H81" s="73" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I81" s="74"/>
       <c r="J81" s="74"/>
@@ -39997,7 +39902,7 @@
       <c r="F82" s="73"/>
       <c r="G82" s="73"/>
       <c r="H82" s="73" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I82" s="74"/>
       <c r="J82" s="74"/>
@@ -40011,7 +39916,7 @@
       <c r="F83" s="73"/>
       <c r="G83" s="73"/>
       <c r="H83" s="73" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I83" s="74"/>
       <c r="J83" s="74"/>
@@ -40025,7 +39930,7 @@
       <c r="F84" s="73"/>
       <c r="G84" s="73"/>
       <c r="H84" s="73" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I84" s="74"/>
       <c r="J84" s="74"/>
